--- a/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
+++ b/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
@@ -2971,7 +2971,7 @@
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="B4:B103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="영문명 입력 오류" error="영문명은 필수이며 최대 100자입니다." promptTitle="영문명 입력 오류" prompt="여권 또는 발급 카드에 사용할 영문명을 입력하세요." type="custom" errorStyle="stop">
-      <formula1>=AND(B4&lt;&gt;"",LEN(TRIM(B4))&lt;=100)</formula1>
+      <formula1>AND(B4&lt;&gt;"",LEN(TRIM(B4))&lt;=100)</formula1>
     </dataValidation>
     <dataValidation sqref="C4:C103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="생년월일 입력 오류" error="미래가 아닌 yyyy-MM-dd 날짜를 입력하세요." promptTitle="생년월일 입력 오류" prompt="필수 항목입니다. 예: 2000-01-31" type="date" errorStyle="stop">
       <formula1>DATE(1900,1,1)</formula1>
@@ -2996,10 +2996,10 @@
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="I4:I103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="이메일 입력 오류" error="유효한 이메일 형식으로 입력하세요." promptTitle="이메일 입력 오류" prompt="필수 항목입니다. 앞뒤 공백 제거 후 소문자로 처리됩니다." type="custom" errorStyle="stop">
-      <formula1>=AND(I4&lt;&gt;"",LEN(I4)&lt;=254,ISNUMBER(SEARCH("@",I4)),ISNUMBER(SEARCH(".",I4,SEARCH("@",I4)+2)),LEFT(I4,1)&lt;&gt;"@",RIGHT(I4,1)&lt;&gt;".")</formula1>
+      <formula1>AND(I4&lt;&gt;"",LEN(I4)&lt;=254,ISNUMBER(SEARCH("@",I4)),ISNUMBER(SEARCH(".",I4,SEARCH("@",I4)+2)),LEFT(I4,1)&lt;&gt;"@",RIGHT(I4,1)&lt;&gt;".")</formula1>
     </dataValidation>
     <dataValidation sqref="J4:J103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="전화번호 입력 오류" error="국가코드를 포함한 E.164 형식으로 입력하세요." promptTitle="전화번호 입력 오류" prompt="필수 항목입니다. 예: +821012345678" type="custom" errorStyle="stop">
-      <formula1>=AND(LEFT(J4,1)="+",LEN(J4)&gt;=3,LEN(J4)&lt;=16,ISNUMBER(--MID(J4,2,15)),MID(J4,2,1)&lt;&gt;"0")</formula1>
+      <formula1>AND(LEFT(J4,1)="+",LEN(J4)&gt;=3,LEN(J4)&lt;=16,ISNUMBER(--MID(J4,2,15)),MID(J4,2,1)&lt;&gt;"0")</formula1>
     </dataValidation>
     <dataValidation sqref="K4:K103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="주소 입력 오류" error="주소는 최대 255자입니다." promptTitle="주소 입력 오류" prompt="선택 항목입니다." type="textLength" errorStyle="stop">
       <formula1>0</formula1>

--- a/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
+++ b/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
@@ -2978,7 +2978,7 @@
       <formula2>TODAY()</formula2>
     </dataValidation>
     <dataValidation sqref="D4:D103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="국적 입력 오류" error="목록의 ISO 2자리 대문자 국가코드를 선택하세요." promptTitle="국적 입력 오류" prompt="필수 항목입니다. 예: KR, US, JP" type="list" errorStyle="stop">
-      <formula1>=CountryCodes</formula1>
+      <formula1>CountryCodes</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="출생시간 입력 오류" error="HH:mm 또는 HH:mm:ss 형식으로 입력하세요." promptTitle="출생시간 입력 오류" prompt="선택 항목입니다. 예: 14:30" type="time" errorStyle="stop">
       <formula1>TIME(0,0,0)</formula1>
@@ -2989,7 +2989,7 @@
       <formula2>200</formula2>
     </dataValidation>
     <dataValidation sqref="G4:G103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="성별 입력 오류" error="MALE 또는 FEMALE을 선택하세요." promptTitle="성별 입력 오류" prompt="필수 항목입니다." type="list" errorStyle="stop">
-      <formula1>=GenderCodes</formula1>
+      <formula1>GenderCodes</formula1>
     </dataValidation>
     <dataValidation sqref="H4:H103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="개별입국날짜 입력 오류" error="yyyy-MM-dd 형식의 날짜를 입력하세요." promptTitle="개별입국날짜 입력 오류" prompt="선택 항목이며, 입력하면 공통 입국날짜보다 우선합니다." type="date" errorStyle="stop">
       <formula1>DATE(1900,1,1)</formula1>

--- a/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
+++ b/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="GenderCodes">'코드목록'!$A$2:$A$3</definedName>
     <definedName name="CountryCodes">'코드목록'!$B$2:$B$250</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'신청자명단'!$A$3:$K$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'신청자명단'!$A$3:$M$103</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'신청자명단'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -353,6 +353,16 @@
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>선택 항목입니다. 자세한 형식과 예시는 작성안내 시트를 확인하세요.</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>필수 항목입니다. 자세한 형식과 예시는 작성안내 시트를 확인하세요.</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0" shapeId="0">
+      <text>
+        <t>필수 항목입니다. 자세한 형식과 예시는 작성안내 시트를 확인하세요.</t>
       </text>
     </comment>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -1149,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1163,6 +1173,8 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1259,6 +1271,16 @@
       <c r="K3" s="4" t="inlineStr">
         <is>
           <t>주소</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>학번</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>학과</t>
         </is>
       </c>
     </row>
@@ -1278,6 +1300,8 @@
       <c r="I4" s="6" t="n"/>
       <c r="J4" s="9" t="n"/>
       <c r="K4" s="6" t="n"/>
+      <c r="L4" s="9" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1295,6 +1319,8 @@
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="6" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1312,6 +1338,8 @@
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="6" t="n"/>
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1329,6 +1357,8 @@
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="6" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1346,6 +1376,8 @@
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="6" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="6" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1363,6 +1395,8 @@
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="6" t="n"/>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="6" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1380,6 +1414,8 @@
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="6" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="6" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1397,6 +1433,8 @@
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="6" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="6" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1414,6 +1452,8 @@
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="6" t="n"/>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="6" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1431,6 +1471,8 @@
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="6" t="n"/>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="6" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1448,6 +1490,8 @@
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="6" t="n"/>
+      <c r="L14" s="9" t="n"/>
+      <c r="M14" s="6" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1465,6 +1509,8 @@
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="6" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="6" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1482,6 +1528,8 @@
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="6" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="6" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1499,6 +1547,8 @@
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="6" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="6" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1516,6 +1566,8 @@
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="6" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="6" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1533,6 +1585,8 @@
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="6" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="6" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1550,6 +1604,8 @@
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="6" t="n"/>
+      <c r="L20" s="9" t="n"/>
+      <c r="M20" s="6" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1567,6 +1623,8 @@
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="6" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="6" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -1584,6 +1642,8 @@
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="6" t="n"/>
+      <c r="L22" s="9" t="n"/>
+      <c r="M22" s="6" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -1601,6 +1661,8 @@
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="6" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="6" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -1618,6 +1680,8 @@
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="6" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="6" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -1635,6 +1699,8 @@
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="6" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="6" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -1652,6 +1718,8 @@
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="6" t="n"/>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="6" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -1669,6 +1737,8 @@
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="6" t="n"/>
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="6" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -1686,6 +1756,8 @@
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="6" t="n"/>
+      <c r="L28" s="9" t="n"/>
+      <c r="M28" s="6" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -1703,6 +1775,8 @@
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="6" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="6" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -1720,6 +1794,8 @@
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="6" t="n"/>
+      <c r="L30" s="9" t="n"/>
+      <c r="M30" s="6" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -1737,6 +1813,8 @@
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="6" t="n"/>
+      <c r="L31" s="9" t="n"/>
+      <c r="M31" s="6" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -1754,6 +1832,8 @@
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="6" t="n"/>
+      <c r="L32" s="9" t="n"/>
+      <c r="M32" s="6" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -1771,6 +1851,8 @@
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="6" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="6" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -1788,6 +1870,8 @@
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="6" t="n"/>
+      <c r="L34" s="9" t="n"/>
+      <c r="M34" s="6" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -1805,6 +1889,8 @@
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="6" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="6" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -1822,6 +1908,8 @@
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="6" t="n"/>
+      <c r="L36" s="9" t="n"/>
+      <c r="M36" s="6" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -1839,6 +1927,8 @@
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="6" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="6" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -1856,6 +1946,8 @@
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="6" t="n"/>
+      <c r="L38" s="9" t="n"/>
+      <c r="M38" s="6" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -1873,6 +1965,8 @@
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="6" t="n"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="6" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -1890,6 +1984,8 @@
       <c r="I40" s="6" t="n"/>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="6" t="n"/>
+      <c r="L40" s="9" t="n"/>
+      <c r="M40" s="6" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -1907,6 +2003,8 @@
       <c r="I41" s="6" t="n"/>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="6" t="n"/>
+      <c r="L41" s="9" t="n"/>
+      <c r="M41" s="6" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -1924,6 +2022,8 @@
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="9" t="n"/>
       <c r="K42" s="6" t="n"/>
+      <c r="L42" s="9" t="n"/>
+      <c r="M42" s="6" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -1941,6 +2041,8 @@
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="9" t="n"/>
       <c r="K43" s="6" t="n"/>
+      <c r="L43" s="9" t="n"/>
+      <c r="M43" s="6" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -1958,6 +2060,8 @@
       <c r="I44" s="6" t="n"/>
       <c r="J44" s="9" t="n"/>
       <c r="K44" s="6" t="n"/>
+      <c r="L44" s="9" t="n"/>
+      <c r="M44" s="6" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
@@ -1975,6 +2079,8 @@
       <c r="I45" s="6" t="n"/>
       <c r="J45" s="9" t="n"/>
       <c r="K45" s="6" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="6" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -1992,6 +2098,8 @@
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="9" t="n"/>
       <c r="K46" s="6" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="6" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -2009,6 +2117,8 @@
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="9" t="n"/>
       <c r="K47" s="6" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="6" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -2026,6 +2136,8 @@
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="9" t="n"/>
       <c r="K48" s="6" t="n"/>
+      <c r="L48" s="9" t="n"/>
+      <c r="M48" s="6" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -2043,6 +2155,8 @@
       <c r="I49" s="6" t="n"/>
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="6" t="n"/>
+      <c r="L49" s="9" t="n"/>
+      <c r="M49" s="6" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -2060,6 +2174,8 @@
       <c r="I50" s="6" t="n"/>
       <c r="J50" s="9" t="n"/>
       <c r="K50" s="6" t="n"/>
+      <c r="L50" s="9" t="n"/>
+      <c r="M50" s="6" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -2077,6 +2193,8 @@
       <c r="I51" s="6" t="n"/>
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="6" t="n"/>
+      <c r="L51" s="9" t="n"/>
+      <c r="M51" s="6" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -2094,6 +2212,8 @@
       <c r="I52" s="6" t="n"/>
       <c r="J52" s="9" t="n"/>
       <c r="K52" s="6" t="n"/>
+      <c r="L52" s="9" t="n"/>
+      <c r="M52" s="6" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -2111,6 +2231,8 @@
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="9" t="n"/>
       <c r="K53" s="6" t="n"/>
+      <c r="L53" s="9" t="n"/>
+      <c r="M53" s="6" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -2128,6 +2250,8 @@
       <c r="I54" s="6" t="n"/>
       <c r="J54" s="9" t="n"/>
       <c r="K54" s="6" t="n"/>
+      <c r="L54" s="9" t="n"/>
+      <c r="M54" s="6" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -2145,6 +2269,8 @@
       <c r="I55" s="6" t="n"/>
       <c r="J55" s="9" t="n"/>
       <c r="K55" s="6" t="n"/>
+      <c r="L55" s="9" t="n"/>
+      <c r="M55" s="6" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -2162,6 +2288,8 @@
       <c r="I56" s="6" t="n"/>
       <c r="J56" s="9" t="n"/>
       <c r="K56" s="6" t="n"/>
+      <c r="L56" s="9" t="n"/>
+      <c r="M56" s="6" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -2179,6 +2307,8 @@
       <c r="I57" s="6" t="n"/>
       <c r="J57" s="9" t="n"/>
       <c r="K57" s="6" t="n"/>
+      <c r="L57" s="9" t="n"/>
+      <c r="M57" s="6" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -2196,6 +2326,8 @@
       <c r="I58" s="6" t="n"/>
       <c r="J58" s="9" t="n"/>
       <c r="K58" s="6" t="n"/>
+      <c r="L58" s="9" t="n"/>
+      <c r="M58" s="6" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -2213,6 +2345,8 @@
       <c r="I59" s="6" t="n"/>
       <c r="J59" s="9" t="n"/>
       <c r="K59" s="6" t="n"/>
+      <c r="L59" s="9" t="n"/>
+      <c r="M59" s="6" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -2230,6 +2364,8 @@
       <c r="I60" s="6" t="n"/>
       <c r="J60" s="9" t="n"/>
       <c r="K60" s="6" t="n"/>
+      <c r="L60" s="9" t="n"/>
+      <c r="M60" s="6" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -2247,6 +2383,8 @@
       <c r="I61" s="6" t="n"/>
       <c r="J61" s="9" t="n"/>
       <c r="K61" s="6" t="n"/>
+      <c r="L61" s="9" t="n"/>
+      <c r="M61" s="6" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -2264,6 +2402,8 @@
       <c r="I62" s="6" t="n"/>
       <c r="J62" s="9" t="n"/>
       <c r="K62" s="6" t="n"/>
+      <c r="L62" s="9" t="n"/>
+      <c r="M62" s="6" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -2281,6 +2421,8 @@
       <c r="I63" s="6" t="n"/>
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="6" t="n"/>
+      <c r="L63" s="9" t="n"/>
+      <c r="M63" s="6" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -2298,6 +2440,8 @@
       <c r="I64" s="6" t="n"/>
       <c r="J64" s="9" t="n"/>
       <c r="K64" s="6" t="n"/>
+      <c r="L64" s="9" t="n"/>
+      <c r="M64" s="6" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -2315,6 +2459,8 @@
       <c r="I65" s="6" t="n"/>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="6" t="n"/>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="6" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -2332,6 +2478,8 @@
       <c r="I66" s="6" t="n"/>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="6" t="n"/>
+      <c r="L66" s="9" t="n"/>
+      <c r="M66" s="6" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -2349,6 +2497,8 @@
       <c r="I67" s="6" t="n"/>
       <c r="J67" s="9" t="n"/>
       <c r="K67" s="6" t="n"/>
+      <c r="L67" s="9" t="n"/>
+      <c r="M67" s="6" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -2366,6 +2516,8 @@
       <c r="I68" s="6" t="n"/>
       <c r="J68" s="9" t="n"/>
       <c r="K68" s="6" t="n"/>
+      <c r="L68" s="9" t="n"/>
+      <c r="M68" s="6" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -2383,6 +2535,8 @@
       <c r="I69" s="6" t="n"/>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="6" t="n"/>
+      <c r="L69" s="9" t="n"/>
+      <c r="M69" s="6" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -2400,6 +2554,8 @@
       <c r="I70" s="6" t="n"/>
       <c r="J70" s="9" t="n"/>
       <c r="K70" s="6" t="n"/>
+      <c r="L70" s="9" t="n"/>
+      <c r="M70" s="6" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -2417,6 +2573,8 @@
       <c r="I71" s="6" t="n"/>
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="6" t="n"/>
+      <c r="L71" s="9" t="n"/>
+      <c r="M71" s="6" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -2434,6 +2592,8 @@
       <c r="I72" s="6" t="n"/>
       <c r="J72" s="9" t="n"/>
       <c r="K72" s="6" t="n"/>
+      <c r="L72" s="9" t="n"/>
+      <c r="M72" s="6" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -2451,6 +2611,8 @@
       <c r="I73" s="6" t="n"/>
       <c r="J73" s="9" t="n"/>
       <c r="K73" s="6" t="n"/>
+      <c r="L73" s="9" t="n"/>
+      <c r="M73" s="6" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -2468,6 +2630,8 @@
       <c r="I74" s="6" t="n"/>
       <c r="J74" s="9" t="n"/>
       <c r="K74" s="6" t="n"/>
+      <c r="L74" s="9" t="n"/>
+      <c r="M74" s="6" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -2485,6 +2649,8 @@
       <c r="I75" s="6" t="n"/>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="6" t="n"/>
+      <c r="L75" s="9" t="n"/>
+      <c r="M75" s="6" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -2502,6 +2668,8 @@
       <c r="I76" s="6" t="n"/>
       <c r="J76" s="9" t="n"/>
       <c r="K76" s="6" t="n"/>
+      <c r="L76" s="9" t="n"/>
+      <c r="M76" s="6" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -2519,6 +2687,8 @@
       <c r="I77" s="6" t="n"/>
       <c r="J77" s="9" t="n"/>
       <c r="K77" s="6" t="n"/>
+      <c r="L77" s="9" t="n"/>
+      <c r="M77" s="6" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -2536,6 +2706,8 @@
       <c r="I78" s="6" t="n"/>
       <c r="J78" s="9" t="n"/>
       <c r="K78" s="6" t="n"/>
+      <c r="L78" s="9" t="n"/>
+      <c r="M78" s="6" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -2553,6 +2725,8 @@
       <c r="I79" s="6" t="n"/>
       <c r="J79" s="9" t="n"/>
       <c r="K79" s="6" t="n"/>
+      <c r="L79" s="9" t="n"/>
+      <c r="M79" s="6" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -2570,6 +2744,8 @@
       <c r="I80" s="6" t="n"/>
       <c r="J80" s="9" t="n"/>
       <c r="K80" s="6" t="n"/>
+      <c r="L80" s="9" t="n"/>
+      <c r="M80" s="6" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -2587,6 +2763,8 @@
       <c r="I81" s="6" t="n"/>
       <c r="J81" s="9" t="n"/>
       <c r="K81" s="6" t="n"/>
+      <c r="L81" s="9" t="n"/>
+      <c r="M81" s="6" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -2604,6 +2782,8 @@
       <c r="I82" s="6" t="n"/>
       <c r="J82" s="9" t="n"/>
       <c r="K82" s="6" t="n"/>
+      <c r="L82" s="9" t="n"/>
+      <c r="M82" s="6" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
@@ -2621,6 +2801,8 @@
       <c r="I83" s="6" t="n"/>
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="6" t="n"/>
+      <c r="L83" s="9" t="n"/>
+      <c r="M83" s="6" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -2638,6 +2820,8 @@
       <c r="I84" s="6" t="n"/>
       <c r="J84" s="9" t="n"/>
       <c r="K84" s="6" t="n"/>
+      <c r="L84" s="9" t="n"/>
+      <c r="M84" s="6" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -2655,6 +2839,8 @@
       <c r="I85" s="6" t="n"/>
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="6" t="n"/>
+      <c r="L85" s="9" t="n"/>
+      <c r="M85" s="6" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -2672,6 +2858,8 @@
       <c r="I86" s="6" t="n"/>
       <c r="J86" s="9" t="n"/>
       <c r="K86" s="6" t="n"/>
+      <c r="L86" s="9" t="n"/>
+      <c r="M86" s="6" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -2689,6 +2877,8 @@
       <c r="I87" s="6" t="n"/>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="6" t="n"/>
+      <c r="L87" s="9" t="n"/>
+      <c r="M87" s="6" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -2706,6 +2896,8 @@
       <c r="I88" s="6" t="n"/>
       <c r="J88" s="9" t="n"/>
       <c r="K88" s="6" t="n"/>
+      <c r="L88" s="9" t="n"/>
+      <c r="M88" s="6" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -2723,6 +2915,8 @@
       <c r="I89" s="6" t="n"/>
       <c r="J89" s="9" t="n"/>
       <c r="K89" s="6" t="n"/>
+      <c r="L89" s="9" t="n"/>
+      <c r="M89" s="6" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -2740,6 +2934,8 @@
       <c r="I90" s="6" t="n"/>
       <c r="J90" s="9" t="n"/>
       <c r="K90" s="6" t="n"/>
+      <c r="L90" s="9" t="n"/>
+      <c r="M90" s="6" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -2757,6 +2953,8 @@
       <c r="I91" s="6" t="n"/>
       <c r="J91" s="9" t="n"/>
       <c r="K91" s="6" t="n"/>
+      <c r="L91" s="9" t="n"/>
+      <c r="M91" s="6" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
@@ -2774,6 +2972,8 @@
       <c r="I92" s="6" t="n"/>
       <c r="J92" s="9" t="n"/>
       <c r="K92" s="6" t="n"/>
+      <c r="L92" s="9" t="n"/>
+      <c r="M92" s="6" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
@@ -2791,6 +2991,8 @@
       <c r="I93" s="6" t="n"/>
       <c r="J93" s="9" t="n"/>
       <c r="K93" s="6" t="n"/>
+      <c r="L93" s="9" t="n"/>
+      <c r="M93" s="6" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -2808,6 +3010,8 @@
       <c r="I94" s="6" t="n"/>
       <c r="J94" s="9" t="n"/>
       <c r="K94" s="6" t="n"/>
+      <c r="L94" s="9" t="n"/>
+      <c r="M94" s="6" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -2825,6 +3029,8 @@
       <c r="I95" s="6" t="n"/>
       <c r="J95" s="9" t="n"/>
       <c r="K95" s="6" t="n"/>
+      <c r="L95" s="9" t="n"/>
+      <c r="M95" s="6" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -2842,6 +3048,8 @@
       <c r="I96" s="6" t="n"/>
       <c r="J96" s="9" t="n"/>
       <c r="K96" s="6" t="n"/>
+      <c r="L96" s="9" t="n"/>
+      <c r="M96" s="6" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
@@ -2859,6 +3067,8 @@
       <c r="I97" s="6" t="n"/>
       <c r="J97" s="9" t="n"/>
       <c r="K97" s="6" t="n"/>
+      <c r="L97" s="9" t="n"/>
+      <c r="M97" s="6" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
@@ -2876,6 +3086,8 @@
       <c r="I98" s="6" t="n"/>
       <c r="J98" s="9" t="n"/>
       <c r="K98" s="6" t="n"/>
+      <c r="L98" s="9" t="n"/>
+      <c r="M98" s="6" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -2893,6 +3105,8 @@
       <c r="I99" s="6" t="n"/>
       <c r="J99" s="9" t="n"/>
       <c r="K99" s="6" t="n"/>
+      <c r="L99" s="9" t="n"/>
+      <c r="M99" s="6" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
@@ -2910,6 +3124,8 @@
       <c r="I100" s="6" t="n"/>
       <c r="J100" s="9" t="n"/>
       <c r="K100" s="6" t="n"/>
+      <c r="L100" s="9" t="n"/>
+      <c r="M100" s="6" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
@@ -2927,6 +3143,8 @@
       <c r="I101" s="6" t="n"/>
       <c r="J101" s="9" t="n"/>
       <c r="K101" s="6" t="n"/>
+      <c r="L101" s="9" t="n"/>
+      <c r="M101" s="6" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
@@ -2944,6 +3162,8 @@
       <c r="I102" s="6" t="n"/>
       <c r="J102" s="9" t="n"/>
       <c r="K102" s="6" t="n"/>
+      <c r="L102" s="9" t="n"/>
+      <c r="M102" s="6" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
@@ -2961,11 +3181,13 @@
       <c r="I103" s="6" t="n"/>
       <c r="J103" s="9" t="n"/>
       <c r="K103" s="6" t="n"/>
+      <c r="L103" s="9" t="n"/>
+      <c r="M103" s="6" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="E0D5"/>
-  <autoFilter ref="A3:K103"/>
-  <dataValidations count="11">
+  <autoFilter ref="A3:M103"/>
+  <dataValidations count="13">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="공통 입국날짜" error="yyyy-MM-dd 형식의 날짜를 입력하세요." promptTitle="공통 입국날짜" prompt="선택 항목입니다. 예: 2026-09-01" type="date" errorStyle="stop">
       <formula1>DATE(1900,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
@@ -3005,6 +3227,12 @@
       <formula1>0</formula1>
       <formula2>255</formula2>
     </dataValidation>
+    <dataValidation sqref="L4:L103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="학번 입력 오류" error="학번은 숫자 1~10자리여야 합니다." promptTitle="학번 입력 오류" prompt="필수 항목이며 텍스트 형식으로 입력하세요." type="custom" errorStyle="stop">
+      <formula1>AND(L4&lt;&gt;"",LEN(L4)&lt;=10,ISNUMBER(--L4),L4=TEXT(--L4,REPT("0",LEN(L4))))</formula1>
+    </dataValidation>
+    <dataValidation sqref="M4:M103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="학과 입력 오류" error="학과는 필수이며 최대 100자입니다." promptTitle="학과 입력 오류" prompt="학교에서 사용하는 학과명을 입력하세요." type="custom" errorStyle="stop">
+      <formula1>AND(M4&lt;&gt;"",LEN(TRIM(M4))&lt;=100)</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -3019,7 +3247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3284,172 +3512,196 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>학번 · 필수</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>학생증에 사용할 숫자 1~10자리 학번을 텍스트로 입력합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>학과 · 필수</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>학교에서 사용하는 학과명을 최대 100자로 입력합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>3. 사진 규칙</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>파일명</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>실제 신청자 행의 사진 번호 + 확장자 형식만 허용합니다. 예: 001.jpg, 002.jpeg, 003.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>형식</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>JPG, JPEG, PNG를 허용하며 확장자 대소문자는 구분하지 않습니다.</t>
-        </is>
-      </c>
+      <c r="B28" s="17" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>크기</t>
+          <t>파일명</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>사진 1개당 최대 2 MiB입니다.</t>
+          <t>실제 신청자 행의 사진 번호 + 확장자 형식만 허용합니다. 예: 001.jpg, 002.jpeg, 003.png</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
+          <t>형식</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>JPG, JPEG, PNG를 허용하며 확장자 대소문자는 구분하지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>크기</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>사진 1개당 최대 2 MiB입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
           <t>해상도</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>EXIF 회전을 적용한 표시 기준 최소 300×400, 권장 600×800~1200×1600입니다.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>정합성</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>사진 누락, Excel에 없는 여분 사진, 001.jpg와 001.png 같은 동일 ID 중복은 모두 신청 전체 실패 사유입니다.</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="34"/>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>4. ZIP 및 파일 제한</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr"/>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>ZIP 구조</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>ZIP 루트에 .xlsx 파일 정확히 1개와 신청자 사진을 둡니다. __MACOSX와 .DS_Store는 무시되지만 하위 폴더 파일은 사진으로 인정하지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>최대 크기</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Excel 5 MiB · 사진 1개 2 MiB · ZIP 250 MiB · 압축 해제 후 전체 250 MiB</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>최대 파일 수</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>운영체제 부산물과 디렉터리를 제외한 유효 파일은 최대 110개입니다.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
+          <t>최대 크기</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Excel 5 MiB · 사진 1개 2 MiB · ZIP 250 MiB · 압축 해제 후 전체 250 MiB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>최대 파일 수</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>운영체제 부산물과 디렉터리를 제외한 유효 파일은 최대 110개입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
           <t>로고·직인</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>학교/기관 로고와 직인은 각각 최대 5 MiB이며 웹 신청 화면에서 별도로 업로드합니다.</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+    <row r="40"/>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>5. 실패 및 개인정보 안내</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr"/>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr"/>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>전체 실패 원칙</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>필수값·형식·사진 번호·사진·양식 버전·헤더 중 하나라도 잘못되면 일부 인원만 접수하지 않고 신청 전체가 실패합니다.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>이메일·전화번호 수집</t>
         </is>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>발급 카드 조회와 국제 안내 발송을 위해 모든 신청자의 이메일과 전화번호를 받습니다. 동일 연락처를 여러 신청자가 공유할 수 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="18" t="inlineStr">
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>구버전 양식</t>
         </is>
       </c>
-      <c r="B42" s="19" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>양식 버전이 지원되지 않으면 공식 공지사항에서 최신 신청 양식을 다시 내려받아 작성해 주세요.</t>
         </is>

--- a/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
+++ b/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="GenderCodes">'코드목록'!$A$2:$A$3</definedName>
     <definedName name="CountryCodes">'코드목록'!$B$2:$B$250</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'신청자명단'!$A$3:$M$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'신청자명단'!$A$3:$K$103</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'신청자명단'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -353,16 +353,6 @@
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>선택 항목입니다. 자세한 형식과 예시는 작성안내 시트를 확인하세요.</t>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0" shapeId="0">
-      <text>
-        <t>필수 항목입니다. 자세한 형식과 예시는 작성안내 시트를 확인하세요.</t>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0" shapeId="0">
-      <text>
-        <t>필수 항목입니다. 자세한 형식과 예시는 작성안내 시트를 확인하세요.</t>
       </text>
     </comment>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -1159,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1173,8 +1163,6 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1271,16 +1259,6 @@
       <c r="K3" s="4" t="inlineStr">
         <is>
           <t>주소</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>학번</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>학과</t>
         </is>
       </c>
     </row>
@@ -1300,8 +1278,6 @@
       <c r="I4" s="6" t="n"/>
       <c r="J4" s="9" t="n"/>
       <c r="K4" s="6" t="n"/>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1319,8 +1295,6 @@
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="6" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1338,8 +1312,6 @@
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="6" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1357,8 +1329,6 @@
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="6" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1376,8 +1346,6 @@
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="6" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="6" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1395,8 +1363,6 @@
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="6" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="6" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1414,8 +1380,6 @@
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="6" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="6" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1433,8 +1397,6 @@
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="6" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="6" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1452,8 +1414,6 @@
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="6" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="6" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1471,8 +1431,6 @@
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="6" t="n"/>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="6" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1490,8 +1448,6 @@
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="6" t="n"/>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="6" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1509,8 +1465,6 @@
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="6" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="6" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1528,8 +1482,6 @@
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="6" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="6" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1547,8 +1499,6 @@
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="6" t="n"/>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="6" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1566,8 +1516,6 @@
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="6" t="n"/>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="6" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1585,8 +1533,6 @@
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="6" t="n"/>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="6" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1604,8 +1550,6 @@
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="6" t="n"/>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="6" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1623,8 +1567,6 @@
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="6" t="n"/>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="6" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -1642,8 +1584,6 @@
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="6" t="n"/>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="6" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -1661,8 +1601,6 @@
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="6" t="n"/>
-      <c r="L23" s="9" t="n"/>
-      <c r="M23" s="6" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -1680,8 +1618,6 @@
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="6" t="n"/>
-      <c r="L24" s="9" t="n"/>
-      <c r="M24" s="6" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -1699,8 +1635,6 @@
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="6" t="n"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="6" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -1718,8 +1652,6 @@
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="6" t="n"/>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="6" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -1737,8 +1669,6 @@
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="6" t="n"/>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="6" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -1756,8 +1686,6 @@
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="6" t="n"/>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="6" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -1775,8 +1703,6 @@
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="6" t="n"/>
-      <c r="L29" s="9" t="n"/>
-      <c r="M29" s="6" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -1794,8 +1720,6 @@
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="6" t="n"/>
-      <c r="L30" s="9" t="n"/>
-      <c r="M30" s="6" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -1813,8 +1737,6 @@
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="6" t="n"/>
-      <c r="L31" s="9" t="n"/>
-      <c r="M31" s="6" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -1832,8 +1754,6 @@
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="6" t="n"/>
-      <c r="L32" s="9" t="n"/>
-      <c r="M32" s="6" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -1851,8 +1771,6 @@
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="6" t="n"/>
-      <c r="L33" s="9" t="n"/>
-      <c r="M33" s="6" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -1870,8 +1788,6 @@
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="6" t="n"/>
-      <c r="L34" s="9" t="n"/>
-      <c r="M34" s="6" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -1889,8 +1805,6 @@
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="6" t="n"/>
-      <c r="L35" s="9" t="n"/>
-      <c r="M35" s="6" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -1908,8 +1822,6 @@
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="6" t="n"/>
-      <c r="L36" s="9" t="n"/>
-      <c r="M36" s="6" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -1927,8 +1839,6 @@
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="6" t="n"/>
-      <c r="L37" s="9" t="n"/>
-      <c r="M37" s="6" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -1946,8 +1856,6 @@
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="6" t="n"/>
-      <c r="L38" s="9" t="n"/>
-      <c r="M38" s="6" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -1965,8 +1873,6 @@
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="6" t="n"/>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="6" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -1984,8 +1890,6 @@
       <c r="I40" s="6" t="n"/>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="6" t="n"/>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="6" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -2003,8 +1907,6 @@
       <c r="I41" s="6" t="n"/>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="6" t="n"/>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="6" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -2022,8 +1924,6 @@
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="9" t="n"/>
       <c r="K42" s="6" t="n"/>
-      <c r="L42" s="9" t="n"/>
-      <c r="M42" s="6" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -2041,8 +1941,6 @@
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="9" t="n"/>
       <c r="K43" s="6" t="n"/>
-      <c r="L43" s="9" t="n"/>
-      <c r="M43" s="6" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -2060,8 +1958,6 @@
       <c r="I44" s="6" t="n"/>
       <c r="J44" s="9" t="n"/>
       <c r="K44" s="6" t="n"/>
-      <c r="L44" s="9" t="n"/>
-      <c r="M44" s="6" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
@@ -2079,8 +1975,6 @@
       <c r="I45" s="6" t="n"/>
       <c r="J45" s="9" t="n"/>
       <c r="K45" s="6" t="n"/>
-      <c r="L45" s="9" t="n"/>
-      <c r="M45" s="6" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -2098,8 +1992,6 @@
       <c r="I46" s="6" t="n"/>
       <c r="J46" s="9" t="n"/>
       <c r="K46" s="6" t="n"/>
-      <c r="L46" s="9" t="n"/>
-      <c r="M46" s="6" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -2117,8 +2009,6 @@
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="9" t="n"/>
       <c r="K47" s="6" t="n"/>
-      <c r="L47" s="9" t="n"/>
-      <c r="M47" s="6" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -2136,8 +2026,6 @@
       <c r="I48" s="6" t="n"/>
       <c r="J48" s="9" t="n"/>
       <c r="K48" s="6" t="n"/>
-      <c r="L48" s="9" t="n"/>
-      <c r="M48" s="6" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -2155,8 +2043,6 @@
       <c r="I49" s="6" t="n"/>
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="6" t="n"/>
-      <c r="L49" s="9" t="n"/>
-      <c r="M49" s="6" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -2174,8 +2060,6 @@
       <c r="I50" s="6" t="n"/>
       <c r="J50" s="9" t="n"/>
       <c r="K50" s="6" t="n"/>
-      <c r="L50" s="9" t="n"/>
-      <c r="M50" s="6" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -2193,8 +2077,6 @@
       <c r="I51" s="6" t="n"/>
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="6" t="n"/>
-      <c r="L51" s="9" t="n"/>
-      <c r="M51" s="6" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -2212,8 +2094,6 @@
       <c r="I52" s="6" t="n"/>
       <c r="J52" s="9" t="n"/>
       <c r="K52" s="6" t="n"/>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="6" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -2231,8 +2111,6 @@
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="9" t="n"/>
       <c r="K53" s="6" t="n"/>
-      <c r="L53" s="9" t="n"/>
-      <c r="M53" s="6" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -2250,8 +2128,6 @@
       <c r="I54" s="6" t="n"/>
       <c r="J54" s="9" t="n"/>
       <c r="K54" s="6" t="n"/>
-      <c r="L54" s="9" t="n"/>
-      <c r="M54" s="6" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -2269,8 +2145,6 @@
       <c r="I55" s="6" t="n"/>
       <c r="J55" s="9" t="n"/>
       <c r="K55" s="6" t="n"/>
-      <c r="L55" s="9" t="n"/>
-      <c r="M55" s="6" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -2288,8 +2162,6 @@
       <c r="I56" s="6" t="n"/>
       <c r="J56" s="9" t="n"/>
       <c r="K56" s="6" t="n"/>
-      <c r="L56" s="9" t="n"/>
-      <c r="M56" s="6" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -2307,8 +2179,6 @@
       <c r="I57" s="6" t="n"/>
       <c r="J57" s="9" t="n"/>
       <c r="K57" s="6" t="n"/>
-      <c r="L57" s="9" t="n"/>
-      <c r="M57" s="6" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -2326,8 +2196,6 @@
       <c r="I58" s="6" t="n"/>
       <c r="J58" s="9" t="n"/>
       <c r="K58" s="6" t="n"/>
-      <c r="L58" s="9" t="n"/>
-      <c r="M58" s="6" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -2345,8 +2213,6 @@
       <c r="I59" s="6" t="n"/>
       <c r="J59" s="9" t="n"/>
       <c r="K59" s="6" t="n"/>
-      <c r="L59" s="9" t="n"/>
-      <c r="M59" s="6" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -2364,8 +2230,6 @@
       <c r="I60" s="6" t="n"/>
       <c r="J60" s="9" t="n"/>
       <c r="K60" s="6" t="n"/>
-      <c r="L60" s="9" t="n"/>
-      <c r="M60" s="6" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -2383,8 +2247,6 @@
       <c r="I61" s="6" t="n"/>
       <c r="J61" s="9" t="n"/>
       <c r="K61" s="6" t="n"/>
-      <c r="L61" s="9" t="n"/>
-      <c r="M61" s="6" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -2402,8 +2264,6 @@
       <c r="I62" s="6" t="n"/>
       <c r="J62" s="9" t="n"/>
       <c r="K62" s="6" t="n"/>
-      <c r="L62" s="9" t="n"/>
-      <c r="M62" s="6" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -2421,8 +2281,6 @@
       <c r="I63" s="6" t="n"/>
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="6" t="n"/>
-      <c r="L63" s="9" t="n"/>
-      <c r="M63" s="6" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -2440,8 +2298,6 @@
       <c r="I64" s="6" t="n"/>
       <c r="J64" s="9" t="n"/>
       <c r="K64" s="6" t="n"/>
-      <c r="L64" s="9" t="n"/>
-      <c r="M64" s="6" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -2459,8 +2315,6 @@
       <c r="I65" s="6" t="n"/>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="6" t="n"/>
-      <c r="L65" s="9" t="n"/>
-      <c r="M65" s="6" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -2478,8 +2332,6 @@
       <c r="I66" s="6" t="n"/>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="6" t="n"/>
-      <c r="L66" s="9" t="n"/>
-      <c r="M66" s="6" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -2497,8 +2349,6 @@
       <c r="I67" s="6" t="n"/>
       <c r="J67" s="9" t="n"/>
       <c r="K67" s="6" t="n"/>
-      <c r="L67" s="9" t="n"/>
-      <c r="M67" s="6" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -2516,8 +2366,6 @@
       <c r="I68" s="6" t="n"/>
       <c r="J68" s="9" t="n"/>
       <c r="K68" s="6" t="n"/>
-      <c r="L68" s="9" t="n"/>
-      <c r="M68" s="6" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -2535,8 +2383,6 @@
       <c r="I69" s="6" t="n"/>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="6" t="n"/>
-      <c r="L69" s="9" t="n"/>
-      <c r="M69" s="6" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -2554,8 +2400,6 @@
       <c r="I70" s="6" t="n"/>
       <c r="J70" s="9" t="n"/>
       <c r="K70" s="6" t="n"/>
-      <c r="L70" s="9" t="n"/>
-      <c r="M70" s="6" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -2573,8 +2417,6 @@
       <c r="I71" s="6" t="n"/>
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="6" t="n"/>
-      <c r="L71" s="9" t="n"/>
-      <c r="M71" s="6" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -2592,8 +2434,6 @@
       <c r="I72" s="6" t="n"/>
       <c r="J72" s="9" t="n"/>
       <c r="K72" s="6" t="n"/>
-      <c r="L72" s="9" t="n"/>
-      <c r="M72" s="6" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -2611,8 +2451,6 @@
       <c r="I73" s="6" t="n"/>
       <c r="J73" s="9" t="n"/>
       <c r="K73" s="6" t="n"/>
-      <c r="L73" s="9" t="n"/>
-      <c r="M73" s="6" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -2630,8 +2468,6 @@
       <c r="I74" s="6" t="n"/>
       <c r="J74" s="9" t="n"/>
       <c r="K74" s="6" t="n"/>
-      <c r="L74" s="9" t="n"/>
-      <c r="M74" s="6" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -2649,8 +2485,6 @@
       <c r="I75" s="6" t="n"/>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="6" t="n"/>
-      <c r="L75" s="9" t="n"/>
-      <c r="M75" s="6" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -2668,8 +2502,6 @@
       <c r="I76" s="6" t="n"/>
       <c r="J76" s="9" t="n"/>
       <c r="K76" s="6" t="n"/>
-      <c r="L76" s="9" t="n"/>
-      <c r="M76" s="6" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -2687,8 +2519,6 @@
       <c r="I77" s="6" t="n"/>
       <c r="J77" s="9" t="n"/>
       <c r="K77" s="6" t="n"/>
-      <c r="L77" s="9" t="n"/>
-      <c r="M77" s="6" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -2706,8 +2536,6 @@
       <c r="I78" s="6" t="n"/>
       <c r="J78" s="9" t="n"/>
       <c r="K78" s="6" t="n"/>
-      <c r="L78" s="9" t="n"/>
-      <c r="M78" s="6" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -2725,8 +2553,6 @@
       <c r="I79" s="6" t="n"/>
       <c r="J79" s="9" t="n"/>
       <c r="K79" s="6" t="n"/>
-      <c r="L79" s="9" t="n"/>
-      <c r="M79" s="6" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -2744,8 +2570,6 @@
       <c r="I80" s="6" t="n"/>
       <c r="J80" s="9" t="n"/>
       <c r="K80" s="6" t="n"/>
-      <c r="L80" s="9" t="n"/>
-      <c r="M80" s="6" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -2763,8 +2587,6 @@
       <c r="I81" s="6" t="n"/>
       <c r="J81" s="9" t="n"/>
       <c r="K81" s="6" t="n"/>
-      <c r="L81" s="9" t="n"/>
-      <c r="M81" s="6" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -2782,8 +2604,6 @@
       <c r="I82" s="6" t="n"/>
       <c r="J82" s="9" t="n"/>
       <c r="K82" s="6" t="n"/>
-      <c r="L82" s="9" t="n"/>
-      <c r="M82" s="6" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
@@ -2801,8 +2621,6 @@
       <c r="I83" s="6" t="n"/>
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="6" t="n"/>
-      <c r="L83" s="9" t="n"/>
-      <c r="M83" s="6" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -2820,8 +2638,6 @@
       <c r="I84" s="6" t="n"/>
       <c r="J84" s="9" t="n"/>
       <c r="K84" s="6" t="n"/>
-      <c r="L84" s="9" t="n"/>
-      <c r="M84" s="6" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -2839,8 +2655,6 @@
       <c r="I85" s="6" t="n"/>
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="6" t="n"/>
-      <c r="L85" s="9" t="n"/>
-      <c r="M85" s="6" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -2858,8 +2672,6 @@
       <c r="I86" s="6" t="n"/>
       <c r="J86" s="9" t="n"/>
       <c r="K86" s="6" t="n"/>
-      <c r="L86" s="9" t="n"/>
-      <c r="M86" s="6" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -2877,8 +2689,6 @@
       <c r="I87" s="6" t="n"/>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="6" t="n"/>
-      <c r="L87" s="9" t="n"/>
-      <c r="M87" s="6" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -2896,8 +2706,6 @@
       <c r="I88" s="6" t="n"/>
       <c r="J88" s="9" t="n"/>
       <c r="K88" s="6" t="n"/>
-      <c r="L88" s="9" t="n"/>
-      <c r="M88" s="6" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -2915,8 +2723,6 @@
       <c r="I89" s="6" t="n"/>
       <c r="J89" s="9" t="n"/>
       <c r="K89" s="6" t="n"/>
-      <c r="L89" s="9" t="n"/>
-      <c r="M89" s="6" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -2934,8 +2740,6 @@
       <c r="I90" s="6" t="n"/>
       <c r="J90" s="9" t="n"/>
       <c r="K90" s="6" t="n"/>
-      <c r="L90" s="9" t="n"/>
-      <c r="M90" s="6" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -2953,8 +2757,6 @@
       <c r="I91" s="6" t="n"/>
       <c r="J91" s="9" t="n"/>
       <c r="K91" s="6" t="n"/>
-      <c r="L91" s="9" t="n"/>
-      <c r="M91" s="6" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
@@ -2972,8 +2774,6 @@
       <c r="I92" s="6" t="n"/>
       <c r="J92" s="9" t="n"/>
       <c r="K92" s="6" t="n"/>
-      <c r="L92" s="9" t="n"/>
-      <c r="M92" s="6" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
@@ -2991,8 +2791,6 @@
       <c r="I93" s="6" t="n"/>
       <c r="J93" s="9" t="n"/>
       <c r="K93" s="6" t="n"/>
-      <c r="L93" s="9" t="n"/>
-      <c r="M93" s="6" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -3010,8 +2808,6 @@
       <c r="I94" s="6" t="n"/>
       <c r="J94" s="9" t="n"/>
       <c r="K94" s="6" t="n"/>
-      <c r="L94" s="9" t="n"/>
-      <c r="M94" s="6" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -3029,8 +2825,6 @@
       <c r="I95" s="6" t="n"/>
       <c r="J95" s="9" t="n"/>
       <c r="K95" s="6" t="n"/>
-      <c r="L95" s="9" t="n"/>
-      <c r="M95" s="6" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -3048,8 +2842,6 @@
       <c r="I96" s="6" t="n"/>
       <c r="J96" s="9" t="n"/>
       <c r="K96" s="6" t="n"/>
-      <c r="L96" s="9" t="n"/>
-      <c r="M96" s="6" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
@@ -3067,8 +2859,6 @@
       <c r="I97" s="6" t="n"/>
       <c r="J97" s="9" t="n"/>
       <c r="K97" s="6" t="n"/>
-      <c r="L97" s="9" t="n"/>
-      <c r="M97" s="6" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
@@ -3086,8 +2876,6 @@
       <c r="I98" s="6" t="n"/>
       <c r="J98" s="9" t="n"/>
       <c r="K98" s="6" t="n"/>
-      <c r="L98" s="9" t="n"/>
-      <c r="M98" s="6" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -3105,8 +2893,6 @@
       <c r="I99" s="6" t="n"/>
       <c r="J99" s="9" t="n"/>
       <c r="K99" s="6" t="n"/>
-      <c r="L99" s="9" t="n"/>
-      <c r="M99" s="6" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
@@ -3124,8 +2910,6 @@
       <c r="I100" s="6" t="n"/>
       <c r="J100" s="9" t="n"/>
       <c r="K100" s="6" t="n"/>
-      <c r="L100" s="9" t="n"/>
-      <c r="M100" s="6" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
@@ -3143,8 +2927,6 @@
       <c r="I101" s="6" t="n"/>
       <c r="J101" s="9" t="n"/>
       <c r="K101" s="6" t="n"/>
-      <c r="L101" s="9" t="n"/>
-      <c r="M101" s="6" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
@@ -3162,8 +2944,6 @@
       <c r="I102" s="6" t="n"/>
       <c r="J102" s="9" t="n"/>
       <c r="K102" s="6" t="n"/>
-      <c r="L102" s="9" t="n"/>
-      <c r="M102" s="6" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
@@ -3181,13 +2961,11 @@
       <c r="I103" s="6" t="n"/>
       <c r="J103" s="9" t="n"/>
       <c r="K103" s="6" t="n"/>
-      <c r="L103" s="9" t="n"/>
-      <c r="M103" s="6" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="E0D5"/>
-  <autoFilter ref="A3:M103"/>
-  <dataValidations count="13">
+  <autoFilter ref="A3:K103"/>
+  <dataValidations count="11">
     <dataValidation sqref="B1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="공통 입국날짜" error="yyyy-MM-dd 형식의 날짜를 입력하세요." promptTitle="공통 입국날짜" prompt="선택 항목입니다. 예: 2026-09-01" type="date" errorStyle="stop">
       <formula1>DATE(1900,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
@@ -3227,12 +3005,6 @@
       <formula1>0</formula1>
       <formula2>255</formula2>
     </dataValidation>
-    <dataValidation sqref="L4:L103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="학번 입력 오류" error="학번은 숫자 1~10자리여야 합니다." promptTitle="학번 입력 오류" prompt="필수 항목이며 텍스트 형식으로 입력하세요." type="custom" errorStyle="stop">
-      <formula1>AND(L4&lt;&gt;"",LEN(L4)&lt;=10,ISNUMBER(--L4),L4=TEXT(--L4,REPT("0",LEN(L4))))</formula1>
-    </dataValidation>
-    <dataValidation sqref="M4:M103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="학과 입력 오류" error="학과는 필수이며 최대 100자입니다." promptTitle="학과 입력 오류" prompt="학교에서 사용하는 학과명을 입력하세요." type="custom" errorStyle="stop">
-      <formula1>AND(M4&lt;&gt;"",LEN(TRIM(M4))&lt;=100)</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -3247,7 +3019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3512,196 +3284,172 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>학번 · 필수</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>학생증에 사용할 숫자 1~10자리 학번을 텍스트로 입력합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>학과 · 필수</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>학교에서 사용하는 학과명을 최대 100자로 입력합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="25"/>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>3. 사진 규칙</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr"/>
+      <c r="B26" s="17" t="inlineStr"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>파일명</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>실제 신청자 행의 사진 번호 + 확장자 형식만 허용합니다. 예: 001.jpg, 002.jpeg, 003.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>형식</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>JPG, JPEG, PNG를 허용하며 확장자 대소문자는 구분하지 않습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>파일명</t>
+          <t>크기</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>실제 신청자 행의 사진 번호 + 확장자 형식만 허용합니다. 예: 001.jpg, 002.jpeg, 003.png</t>
+          <t>사진 1개당 최대 2 MiB입니다.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>형식</t>
+          <t>해상도</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>JPG, JPEG, PNG를 허용하며 확장자 대소문자는 구분하지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
+          <t>EXIF 회전을 적용한 표시 기준 최소 300×400, 권장 600×800~1200×1600입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>크기</t>
+          <t>정합성</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>사진 1개당 최대 2 MiB입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>해상도</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>EXIF 회전을 적용한 표시 기준 최소 300×400, 권장 600×800~1200×1600입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>정합성</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
           <t>사진 누락, Excel에 없는 여분 사진, 001.jpg와 001.png 같은 동일 ID 중복은 모두 신청 전체 실패 사유입니다.</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="32"/>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>4. ZIP 및 파일 제한</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr"/>
-    </row>
-    <row r="36" ht="36" customHeight="1">
+      <c r="B33" s="17" t="inlineStr"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>ZIP 구조</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>ZIP 루트에 .xlsx 파일 정확히 1개와 신청자 사진을 둡니다. __MACOSX와 .DS_Store는 무시되지만 하위 폴더 파일은 사진으로 인정하지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>최대 크기</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Excel 5 MiB · 사진 1개 2 MiB · ZIP 250 MiB · 압축 해제 후 전체 250 MiB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>ZIP 구조</t>
+          <t>최대 파일 수</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>ZIP 루트에 .xlsx 파일 정확히 1개와 신청자 사진을 둡니다. __MACOSX와 .DS_Store는 무시되지만 하위 폴더 파일은 사진으로 인정하지 않습니다.</t>
+          <t>운영체제 부산물과 디렉터리를 제외한 유효 파일은 최대 110개입니다.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>최대 크기</t>
+          <t>로고·직인</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>Excel 5 MiB · 사진 1개 2 MiB · ZIP 250 MiB · 압축 해제 후 전체 250 MiB</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>최대 파일 수</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>운영체제 부산물과 디렉터리를 제외한 유효 파일은 최대 110개입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>로고·직인</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
           <t>학교/기관 로고와 직인은 각각 최대 5 MiB이며 웹 신청 화면에서 별도로 업로드합니다.</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="38"/>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>5. 실패 및 개인정보 안내</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr"/>
-    </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr"/>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>전체 실패 원칙</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>필수값·형식·사진 번호·사진·양식 버전·헤더 중 하나라도 잘못되면 일부 인원만 접수하지 않고 신청 전체가 실패합니다.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="18" t="inlineStr">
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>이메일·전화번호 수집</t>
         </is>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>발급 카드 조회와 국제 안내 발송을 위해 모든 신청자의 이메일과 전화번호를 받습니다. 동일 연락처를 여러 신청자가 공유할 수 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>구버전 양식</t>
         </is>
       </c>
-      <c r="B44" s="19" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>양식 버전이 지원되지 않으면 공식 공지사항에서 최신 신청 양식을 다시 내려받아 작성해 주세요.</t>
         </is>

--- a/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
+++ b/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.1.xlsx
@@ -327,7 +327,7 @@
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
-        <t>선택 항목입니다. 자세한 형식과 예시는 작성안내 시트를 확인하세요.</t>
+        <t>필수 항목입니다. 자세한 형식과 예시는 작성안내 시트를 확인하세요.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>국적</t>
+          <t>출생국가</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -2977,16 +2977,15 @@
       <formula1>DATE(1900,1,1)</formula1>
       <formula2>TODAY()</formula2>
     </dataValidation>
-    <dataValidation sqref="D4:D103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="국적 입력 오류" error="목록의 ISO 2자리 대문자 국가코드를 선택하세요." promptTitle="국적 입력 오류" prompt="필수 항목입니다. 예: KR, US, JP" type="list" errorStyle="stop">
+    <dataValidation sqref="D4:D103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="출생국가 입력 오류" error="목록의 ISO 2자리 대문자 국가코드를 선택하세요." promptTitle="출생국가 입력 오류" prompt="필수 항목입니다. 예: KR, US, JP" type="list" errorStyle="stop">
       <formula1>CountryCodes</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="출생시간 입력 오류" error="HH:mm 또는 HH:mm:ss 형식으로 입력하세요." promptTitle="출생시간 입력 오류" prompt="선택 항목입니다. 예: 14:30" type="time" errorStyle="stop">
       <formula1>TIME(0,0,0)</formula1>
       <formula2>TIME(23,59,59)</formula2>
     </dataValidation>
-    <dataValidation sqref="F4:F103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="출생지역 입력 오류" error="출생지역은 최대 200자입니다." promptTitle="출생지역 입력 오류" prompt="선택 항목입니다." type="textLength" errorStyle="stop">
-      <formula1>0</formula1>
-      <formula2>200</formula2>
+    <dataValidation sqref="F4:F103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="출생지역 입력 오류" error="출생지역은 필수이며 태어난 도시명을 최대 200자로 입력해야 합니다." promptTitle="출생지역 입력 오류" prompt="태어난 도시명을 입력하세요. 예: Chicago, London, Tokyo, Beijing, Los Angeles" type="custom" errorStyle="stop">
+      <formula1>AND(F4&lt;&gt;"",LEN(TRIM(F4))&lt;=200)</formula1>
     </dataValidation>
     <dataValidation sqref="G4:G103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="성별 입력 오류" error="MALE 또는 FEMALE을 선택하세요." promptTitle="성별 입력 오류" prompt="필수 항목입니다." type="list" errorStyle="stop">
       <formula1>GenderCodes</formula1>
@@ -3191,7 +3190,7 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>국적 · 필수</t>
+          <t>출생국가 · 필수</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
@@ -3212,15 +3211,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>출생지역 · 선택</t>
+          <t>출생지역(출신지역) · 필수</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>최대 200자로 입력합니다.</t>
+          <t>태어난 도시명을 최대 200자로 입력합니다. 예: Chicago, London, Tokyo, Beijing, Los Angeles</t>
         </is>
       </c>
     </row>
